--- a/tests/Common_Test_Cases/建设项目_个性化用例.xlsx
+++ b/tests/Common_Test_Cases/建设项目_个性化用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Auto_Testing\UI-Smoke-Testing\tests\Common_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B651B94-455E-492D-B0DD-7C6A77FB7D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D067B59-F651-4BD3-B587-0DE2C092C977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="59">
   <si>
     <t>用例ID</t>
   </si>
@@ -220,6 +220,10 @@
   <si>
     <t>”？”提示：内容原则上包含项目背景、必要性、建设内容、规模、周期、市场前景、技术可行性、预算、资金筹措、回报、风险分析等。</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动化执行方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -440,7 +444,43 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFE5E7EB"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFE5E7EB"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF7F6000"/>
@@ -517,9 +557,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B08AE844-4FE0-4007-9FD9-9332A80889F9}" name="OptimizedAddCases" displayName="OptimizedAddCases" ref="A1:N122" totalsRowShown="0">
-  <autoFilter ref="A1:N122" xr:uid="{B08AE844-4FE0-4007-9FD9-9332A80889F9}"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B08AE844-4FE0-4007-9FD9-9332A80889F9}" name="OptimizedAddCases" displayName="OptimizedAddCases" ref="A1:O122" totalsRowShown="0">
+  <autoFilter ref="A1:O122" xr:uid="{B08AE844-4FE0-4007-9FD9-9332A80889F9}"/>
+  <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{2B97DE63-BA9E-4460-B3C0-9AA2188B3AAE}" name="用例ID"/>
     <tableColumn id="2" xr3:uid="{3651ADE7-7A92-40D3-93BA-1A7645696A5A}" name="功能"/>
     <tableColumn id="3" xr3:uid="{04DFDEA8-323E-4040-BED1-E14D9400CC23}" name="字段/控件"/>
@@ -530,6 +570,7 @@
     <tableColumn id="8" xr3:uid="{6512512F-DD54-4049-87F4-E7C213779827}" name="预期结果"/>
     <tableColumn id="9" xr3:uid="{934FFC46-C527-48F3-92DE-A699B77142B5}" name="优先级"/>
     <tableColumn id="10" xr3:uid="{1A5D63AF-4864-467E-AF6F-302AE1D22C24}" name="是否自动化"/>
+    <tableColumn id="15" xr3:uid="{7F9C8BE8-00E0-4E4E-B870-27935BC02D6F}" name="自动化执行方式" dataDxfId="0"/>
     <tableColumn id="11" xr3:uid="{CB104130-AC1C-4391-8144-79CB45D4EAA4}" name="执行结果"/>
     <tableColumn id="12" xr3:uid="{2C556962-D51B-43AE-B4E4-97C77DC2AFC7}" name="测试人员"/>
     <tableColumn id="13" xr3:uid="{64E9F646-5326-4C9D-92BA-25BABA77BDCC}" name="测试日期"/>
@@ -812,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N122"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -824,13 +865,15 @@
     <col min="7" max="7" width="42" customWidth="1"/>
     <col min="8" max="8" width="46" customWidth="1"/>
     <col min="9" max="9" width="10" customWidth="1"/>
-    <col min="10" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="30" customWidth="1"/>
+    <col min="10" max="10" width="11" customWidth="1"/>
+    <col min="11" max="11" width="13.46484375" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="14" max="14" width="13" customWidth="1"/>
+    <col min="15" max="15" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1">
+    <row r="1" spans="1:15" ht="30" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -862,19 +905,22 @@
         <v>14</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="42" customHeight="1">
+    <row r="2" spans="1:15" ht="42" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
@@ -905,14 +951,15 @@
       <c r="J2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="4"/>
+      <c r="L2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" ht="42" customHeight="1">
+      <c r="M2" s="4"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="6"/>
+    </row>
+    <row r="3" spans="1:15" ht="42" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>35</v>
       </c>
@@ -943,14 +990,15 @@
       <c r="J3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="4"/>
+      <c r="L3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" ht="42" customHeight="1">
+      <c r="M3" s="4"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" spans="1:15" ht="42" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>36</v>
       </c>
@@ -981,14 +1029,15 @@
       <c r="J4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="42" customHeight="1">
+      <c r="M4" s="4"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" spans="1:15" ht="42" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>37</v>
       </c>
@@ -1019,14 +1068,15 @@
       <c r="J5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" ht="42" customHeight="1">
+      <c r="M5" s="4"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="6"/>
+    </row>
+    <row r="6" spans="1:15" ht="42" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -1039,10 +1089,11 @@
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="42" customHeight="1">
+      <c r="M6" s="4"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="6"/>
+    </row>
+    <row r="7" spans="1:15" ht="42" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -1055,10 +1106,11 @@
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" ht="42" customHeight="1">
+      <c r="M7" s="4"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="6"/>
+    </row>
+    <row r="8" spans="1:15" ht="42" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -1071,10 +1123,11 @@
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" ht="42" customHeight="1">
+      <c r="M8" s="4"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="6"/>
+    </row>
+    <row r="9" spans="1:15" ht="42" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -1087,10 +1140,11 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" ht="42" customHeight="1">
+      <c r="M9" s="4"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="6"/>
+    </row>
+    <row r="10" spans="1:15" ht="42" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -1103,10 +1157,11 @@
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" ht="42" customHeight="1">
+      <c r="M10" s="4"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="6"/>
+    </row>
+    <row r="11" spans="1:15" ht="42" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -1119,10 +1174,11 @@
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" ht="42" customHeight="1">
+      <c r="M11" s="4"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" ht="42" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -1135,10 +1191,11 @@
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
-      <c r="M12" s="5"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="42" customHeight="1">
+      <c r="M12" s="4"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" ht="42" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -1151,10 +1208,11 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" ht="42" customHeight="1">
+      <c r="M13" s="4"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" ht="42" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -1167,10 +1225,11 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" ht="42" customHeight="1">
+      <c r="M14" s="4"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" ht="42" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -1183,10 +1242,11 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="42" customHeight="1">
+      <c r="M15" s="4"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="6"/>
+    </row>
+    <row r="16" spans="1:15" ht="42" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1199,10 +1259,11 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
-      <c r="M16" s="5"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" ht="42" customHeight="1">
+      <c r="M16" s="4"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="6"/>
+    </row>
+    <row r="17" spans="1:15" ht="42" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1215,10 +1276,11 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
-      <c r="M17" s="5"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" ht="42" customHeight="1">
+      <c r="M17" s="4"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="6"/>
+    </row>
+    <row r="18" spans="1:15" ht="42" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1231,10 +1293,11 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
-      <c r="M18" s="5"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" ht="42" customHeight="1">
+      <c r="M18" s="4"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="6"/>
+    </row>
+    <row r="19" spans="1:15" ht="42" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1247,10 +1310,11 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" ht="42" customHeight="1">
+      <c r="M19" s="4"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="6"/>
+    </row>
+    <row r="20" spans="1:15" ht="42" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1263,10 +1327,11 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" ht="42" customHeight="1">
+      <c r="M20" s="4"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="6"/>
+    </row>
+    <row r="21" spans="1:15" ht="42" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1279,10 +1344,11 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" ht="42" customHeight="1">
+      <c r="M21" s="4"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="6"/>
+    </row>
+    <row r="22" spans="1:15" ht="42" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1295,10 +1361,11 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
-      <c r="M22" s="5"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" ht="42" customHeight="1">
+      <c r="M22" s="4"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="6"/>
+    </row>
+    <row r="23" spans="1:15" ht="42" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1311,10 +1378,11 @@
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" ht="42" customHeight="1">
+      <c r="M23" s="4"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="6"/>
+    </row>
+    <row r="24" spans="1:15" ht="42" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1327,10 +1395,11 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" ht="42" customHeight="1">
+      <c r="M24" s="4"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="6"/>
+    </row>
+    <row r="25" spans="1:15" ht="42" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1343,10 +1412,11 @@
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" ht="42" customHeight="1">
+      <c r="M25" s="4"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="6"/>
+    </row>
+    <row r="26" spans="1:15" ht="42" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1359,10 +1429,11 @@
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
-      <c r="M26" s="5"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" ht="42" customHeight="1">
+      <c r="M26" s="4"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="6"/>
+    </row>
+    <row r="27" spans="1:15" ht="42" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1375,10 +1446,11 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
-    </row>
-    <row r="28" spans="1:14" ht="42" customHeight="1">
+      <c r="M27" s="4"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="6"/>
+    </row>
+    <row r="28" spans="1:15" ht="42" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1391,10 +1463,11 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="1:14" ht="42" customHeight="1">
+      <c r="M28" s="4"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="6"/>
+    </row>
+    <row r="29" spans="1:15" ht="42" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1407,10 +1480,11 @@
       <c r="J29" s="4"/>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
-      <c r="M29" s="5"/>
-      <c r="N29" s="6"/>
-    </row>
-    <row r="30" spans="1:14" ht="42" customHeight="1">
+      <c r="M29" s="4"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="6"/>
+    </row>
+    <row r="30" spans="1:15" ht="42" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1423,10 +1497,11 @@
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="6"/>
-    </row>
-    <row r="31" spans="1:14" ht="42" customHeight="1">
+      <c r="M30" s="4"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="6"/>
+    </row>
+    <row r="31" spans="1:15" ht="42" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1439,10 +1514,11 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
-      <c r="M31" s="5"/>
-      <c r="N31" s="6"/>
-    </row>
-    <row r="32" spans="1:14" ht="42" customHeight="1">
+      <c r="M31" s="4"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="6"/>
+    </row>
+    <row r="32" spans="1:15" ht="42" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1455,10 +1531,11 @@
       <c r="J32" s="4"/>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
-      <c r="M32" s="5"/>
-      <c r="N32" s="6"/>
-    </row>
-    <row r="33" spans="1:14" ht="42" customHeight="1">
+      <c r="M32" s="4"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="6"/>
+    </row>
+    <row r="33" spans="1:15" ht="42" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1471,10 +1548,11 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-    </row>
-    <row r="34" spans="1:14" ht="42" customHeight="1">
+      <c r="M33" s="4"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="6"/>
+    </row>
+    <row r="34" spans="1:15" ht="42" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1487,10 +1565,11 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
-      <c r="M34" s="5"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" ht="42" customHeight="1">
+      <c r="M34" s="4"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="6"/>
+    </row>
+    <row r="35" spans="1:15" ht="42" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1503,10 +1582,11 @@
       <c r="J35" s="4"/>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" ht="42" customHeight="1">
+      <c r="M35" s="4"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="6"/>
+    </row>
+    <row r="36" spans="1:15" ht="42" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1519,10 +1599,11 @@
       <c r="J36" s="4"/>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" ht="42" customHeight="1">
+      <c r="M36" s="4"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="6"/>
+    </row>
+    <row r="37" spans="1:15" ht="42" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1535,10 +1616,11 @@
       <c r="J37" s="4"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="6"/>
-    </row>
-    <row r="38" spans="1:14" ht="42" customHeight="1">
+      <c r="M37" s="4"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="6"/>
+    </row>
+    <row r="38" spans="1:15" ht="42" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1551,10 +1633,11 @@
       <c r="J38" s="4"/>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="6"/>
-    </row>
-    <row r="39" spans="1:14" ht="42" customHeight="1">
+      <c r="M38" s="4"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="6"/>
+    </row>
+    <row r="39" spans="1:15" ht="42" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1567,10 +1650,11 @@
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-    </row>
-    <row r="40" spans="1:14" ht="42" customHeight="1">
+      <c r="M39" s="4"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="6"/>
+    </row>
+    <row r="40" spans="1:15" ht="42" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1583,10 +1667,11 @@
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="6"/>
-    </row>
-    <row r="41" spans="1:14" ht="42" customHeight="1">
+      <c r="M40" s="4"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="6"/>
+    </row>
+    <row r="41" spans="1:15" ht="42" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1599,10 +1684,11 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="6"/>
-    </row>
-    <row r="42" spans="1:14" ht="42" customHeight="1">
+      <c r="M41" s="4"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="6"/>
+    </row>
+    <row r="42" spans="1:15" ht="42" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1615,10 +1701,11 @@
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-    </row>
-    <row r="43" spans="1:14" ht="42" customHeight="1">
+      <c r="M42" s="4"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="6"/>
+    </row>
+    <row r="43" spans="1:15" ht="42" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1631,10 +1718,11 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
-    </row>
-    <row r="44" spans="1:14" ht="42" customHeight="1">
+      <c r="M43" s="4"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="6"/>
+    </row>
+    <row r="44" spans="1:15" ht="42" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1647,10 +1735,11 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
-      <c r="M44" s="5"/>
-      <c r="N44" s="6"/>
-    </row>
-    <row r="45" spans="1:14" ht="42" customHeight="1">
+      <c r="M44" s="4"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="6"/>
+    </row>
+    <row r="45" spans="1:15" ht="42" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1663,10 +1752,11 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="6"/>
-    </row>
-    <row r="46" spans="1:14" ht="42" customHeight="1">
+      <c r="M45" s="4"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="6"/>
+    </row>
+    <row r="46" spans="1:15" ht="42" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1679,10 +1769,11 @@
       <c r="J46" s="4"/>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
-      <c r="M46" s="5"/>
-      <c r="N46" s="6"/>
-    </row>
-    <row r="47" spans="1:14" ht="42" customHeight="1">
+      <c r="M46" s="4"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="6"/>
+    </row>
+    <row r="47" spans="1:15" ht="42" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1695,10 +1786,11 @@
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
-      <c r="M47" s="5"/>
-      <c r="N47" s="6"/>
-    </row>
-    <row r="48" spans="1:14" ht="42" customHeight="1">
+      <c r="M47" s="4"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="6"/>
+    </row>
+    <row r="48" spans="1:15" ht="42" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1711,10 +1803,11 @@
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
-      <c r="M48" s="5"/>
-      <c r="N48" s="6"/>
-    </row>
-    <row r="49" spans="1:14" ht="42" customHeight="1">
+      <c r="M48" s="4"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="6"/>
+    </row>
+    <row r="49" spans="1:15" ht="42" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1727,10 +1820,11 @@
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="6"/>
-    </row>
-    <row r="50" spans="1:14" ht="42" customHeight="1">
+      <c r="M49" s="4"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="6"/>
+    </row>
+    <row r="50" spans="1:15" ht="42" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -1743,10 +1837,11 @@
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-    </row>
-    <row r="51" spans="1:14" ht="42" customHeight="1">
+      <c r="M50" s="4"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="6"/>
+    </row>
+    <row r="51" spans="1:15" ht="42" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -1759,10 +1854,11 @@
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-    </row>
-    <row r="52" spans="1:14" ht="42" customHeight="1">
+      <c r="M51" s="4"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="6"/>
+    </row>
+    <row r="52" spans="1:15" ht="42" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1775,10 +1871,11 @@
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="6"/>
-    </row>
-    <row r="53" spans="1:14" ht="42" customHeight="1">
+      <c r="M52" s="4"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="6"/>
+    </row>
+    <row r="53" spans="1:15" ht="42" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -1791,10 +1888,11 @@
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
-      <c r="M53" s="5"/>
-      <c r="N53" s="6"/>
-    </row>
-    <row r="54" spans="1:14" ht="42" customHeight="1">
+      <c r="M53" s="4"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="6"/>
+    </row>
+    <row r="54" spans="1:15" ht="42" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -1807,10 +1905,11 @@
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="6"/>
-    </row>
-    <row r="55" spans="1:14" ht="42" customHeight="1">
+      <c r="M54" s="4"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="6"/>
+    </row>
+    <row r="55" spans="1:15" ht="42" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -1823,10 +1922,11 @@
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-    </row>
-    <row r="56" spans="1:14" ht="42" customHeight="1">
+      <c r="M55" s="4"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="6"/>
+    </row>
+    <row r="56" spans="1:15" ht="42" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -1839,10 +1939,11 @@
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
-      <c r="M56" s="5"/>
-      <c r="N56" s="6"/>
-    </row>
-    <row r="57" spans="1:14" ht="42" customHeight="1">
+      <c r="M56" s="4"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="6"/>
+    </row>
+    <row r="57" spans="1:15" ht="42" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -1855,10 +1956,11 @@
       <c r="J57" s="4"/>
       <c r="K57" s="4"/>
       <c r="L57" s="4"/>
-      <c r="M57" s="5"/>
-      <c r="N57" s="6"/>
-    </row>
-    <row r="58" spans="1:14" ht="42" customHeight="1">
+      <c r="M57" s="4"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="6"/>
+    </row>
+    <row r="58" spans="1:15" ht="42" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -1871,10 +1973,11 @@
       <c r="J58" s="4"/>
       <c r="K58" s="4"/>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
-    </row>
-    <row r="59" spans="1:14" ht="42" customHeight="1">
+      <c r="M58" s="4"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="6"/>
+    </row>
+    <row r="59" spans="1:15" ht="42" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -1887,10 +1990,11 @@
       <c r="J59" s="4"/>
       <c r="K59" s="4"/>
       <c r="L59" s="4"/>
-      <c r="M59" s="5"/>
-      <c r="N59" s="6"/>
-    </row>
-    <row r="60" spans="1:14" ht="42" customHeight="1">
+      <c r="M59" s="4"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="6"/>
+    </row>
+    <row r="60" spans="1:15" ht="42" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -1903,10 +2007,11 @@
       <c r="J60" s="4"/>
       <c r="K60" s="4"/>
       <c r="L60" s="4"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="6"/>
-    </row>
-    <row r="61" spans="1:14" ht="42" customHeight="1">
+      <c r="M60" s="4"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="6"/>
+    </row>
+    <row r="61" spans="1:15" ht="42" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -1919,10 +2024,11 @@
       <c r="J61" s="4"/>
       <c r="K61" s="4"/>
       <c r="L61" s="4"/>
-      <c r="M61" s="5"/>
-      <c r="N61" s="6"/>
-    </row>
-    <row r="62" spans="1:14" ht="42" customHeight="1">
+      <c r="M61" s="4"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="6"/>
+    </row>
+    <row r="62" spans="1:15" ht="42" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -1935,10 +2041,11 @@
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6"/>
-    </row>
-    <row r="63" spans="1:14" ht="42" customHeight="1">
+      <c r="M62" s="4"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="6"/>
+    </row>
+    <row r="63" spans="1:15" ht="42" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -1951,10 +2058,11 @@
       <c r="J63" s="4"/>
       <c r="K63" s="4"/>
       <c r="L63" s="4"/>
-      <c r="M63" s="5"/>
-      <c r="N63" s="6"/>
-    </row>
-    <row r="64" spans="1:14" ht="42" customHeight="1">
+      <c r="M63" s="4"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="6"/>
+    </row>
+    <row r="64" spans="1:15" ht="42" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -1967,10 +2075,11 @@
       <c r="J64" s="4"/>
       <c r="K64" s="4"/>
       <c r="L64" s="4"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="6"/>
-    </row>
-    <row r="65" spans="1:14" ht="42" customHeight="1">
+      <c r="M64" s="4"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="6"/>
+    </row>
+    <row r="65" spans="1:15" ht="42" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -1983,10 +2092,11 @@
       <c r="J65" s="4"/>
       <c r="K65" s="4"/>
       <c r="L65" s="4"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="6"/>
-    </row>
-    <row r="66" spans="1:14" ht="42" customHeight="1">
+      <c r="M65" s="4"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="6"/>
+    </row>
+    <row r="66" spans="1:15" ht="42" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -1999,10 +2109,11 @@
       <c r="J66" s="4"/>
       <c r="K66" s="4"/>
       <c r="L66" s="4"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="6"/>
-    </row>
-    <row r="67" spans="1:14" ht="42" customHeight="1">
+      <c r="M66" s="4"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="6"/>
+    </row>
+    <row r="67" spans="1:15" ht="42" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2015,10 +2126,11 @@
       <c r="J67" s="4"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
-      <c r="M67" s="5"/>
-      <c r="N67" s="6"/>
-    </row>
-    <row r="68" spans="1:14" ht="42" customHeight="1">
+      <c r="M67" s="4"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="6"/>
+    </row>
+    <row r="68" spans="1:15" ht="42" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2031,10 +2143,11 @@
       <c r="J68" s="4"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
-      <c r="M68" s="5"/>
-      <c r="N68" s="6"/>
-    </row>
-    <row r="69" spans="1:14" ht="42" customHeight="1">
+      <c r="M68" s="4"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="6"/>
+    </row>
+    <row r="69" spans="1:15" ht="42" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2047,10 +2160,11 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="6"/>
-    </row>
-    <row r="70" spans="1:14" ht="42" customHeight="1">
+      <c r="M69" s="4"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="6"/>
+    </row>
+    <row r="70" spans="1:15" ht="42" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2063,10 +2177,11 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="6"/>
-    </row>
-    <row r="71" spans="1:14" ht="42" customHeight="1">
+      <c r="M70" s="4"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="6"/>
+    </row>
+    <row r="71" spans="1:15" ht="42" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2079,10 +2194,11 @@
       <c r="J71" s="4"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-    </row>
-    <row r="72" spans="1:14" ht="42" customHeight="1">
+      <c r="M71" s="4"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="6"/>
+    </row>
+    <row r="72" spans="1:15" ht="42" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2095,10 +2211,11 @@
       <c r="J72" s="4"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
-      <c r="M72" s="5"/>
-      <c r="N72" s="6"/>
-    </row>
-    <row r="73" spans="1:14" ht="42" customHeight="1">
+      <c r="M72" s="4"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="6"/>
+    </row>
+    <row r="73" spans="1:15" ht="42" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2111,10 +2228,11 @@
       <c r="J73" s="4"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
-      <c r="M73" s="5"/>
-      <c r="N73" s="6"/>
-    </row>
-    <row r="74" spans="1:14" ht="42" customHeight="1">
+      <c r="M73" s="4"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="6"/>
+    </row>
+    <row r="74" spans="1:15" ht="42" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -2127,10 +2245,11 @@
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
-      <c r="M74" s="5"/>
-      <c r="N74" s="6"/>
-    </row>
-    <row r="75" spans="1:14" ht="42" customHeight="1">
+      <c r="M74" s="4"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="6"/>
+    </row>
+    <row r="75" spans="1:15" ht="42" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -2143,10 +2262,11 @@
       <c r="J75" s="4"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-    </row>
-    <row r="76" spans="1:14" ht="42" customHeight="1">
+      <c r="M75" s="4"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="6"/>
+    </row>
+    <row r="76" spans="1:15" ht="42" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -2159,10 +2279,11 @@
       <c r="J76" s="4"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-    </row>
-    <row r="77" spans="1:14" ht="42" customHeight="1">
+      <c r="M76" s="4"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="6"/>
+    </row>
+    <row r="77" spans="1:15" ht="42" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2175,10 +2296,11 @@
       <c r="J77" s="4"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
-      <c r="M77" s="5"/>
-      <c r="N77" s="6"/>
-    </row>
-    <row r="78" spans="1:14" ht="42" customHeight="1">
+      <c r="M77" s="4"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="6"/>
+    </row>
+    <row r="78" spans="1:15" ht="42" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -2191,10 +2313,11 @@
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
-      <c r="M78" s="5"/>
-      <c r="N78" s="6"/>
-    </row>
-    <row r="79" spans="1:14" ht="42" customHeight="1">
+      <c r="M78" s="4"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="6"/>
+    </row>
+    <row r="79" spans="1:15" ht="42" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -2207,10 +2330,11 @@
       <c r="J79" s="4"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
-      <c r="M79" s="5"/>
-      <c r="N79" s="6"/>
-    </row>
-    <row r="80" spans="1:14" ht="42" customHeight="1">
+      <c r="M79" s="4"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="6"/>
+    </row>
+    <row r="80" spans="1:15" ht="42" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -2223,10 +2347,11 @@
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
-      <c r="M80" s="5"/>
-      <c r="N80" s="6"/>
-    </row>
-    <row r="81" spans="1:14" ht="42" customHeight="1">
+      <c r="M80" s="4"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="6"/>
+    </row>
+    <row r="81" spans="1:15" ht="42" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -2239,10 +2364,11 @@
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
-      <c r="M81" s="5"/>
-      <c r="N81" s="6"/>
-    </row>
-    <row r="82" spans="1:14" ht="42" customHeight="1">
+      <c r="M81" s="4"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="6"/>
+    </row>
+    <row r="82" spans="1:15" ht="42" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -2255,10 +2381,11 @@
       <c r="J82" s="4"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
-      <c r="M82" s="5"/>
-      <c r="N82" s="6"/>
-    </row>
-    <row r="83" spans="1:14" ht="42" customHeight="1">
+      <c r="M82" s="4"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="6"/>
+    </row>
+    <row r="83" spans="1:15" ht="42" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -2271,10 +2398,11 @@
       <c r="J83" s="4"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
-      <c r="M83" s="5"/>
-      <c r="N83" s="6"/>
-    </row>
-    <row r="84" spans="1:14" ht="42" customHeight="1">
+      <c r="M83" s="4"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="6"/>
+    </row>
+    <row r="84" spans="1:15" ht="42" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2287,10 +2415,11 @@
       <c r="J84" s="4"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="6"/>
-    </row>
-    <row r="85" spans="1:14" ht="42" customHeight="1">
+      <c r="M84" s="4"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="6"/>
+    </row>
+    <row r="85" spans="1:15" ht="42" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -2303,10 +2432,11 @@
       <c r="J85" s="4"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
-      <c r="M85" s="5"/>
-      <c r="N85" s="6"/>
-    </row>
-    <row r="86" spans="1:14" ht="42" customHeight="1">
+      <c r="M85" s="4"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="6"/>
+    </row>
+    <row r="86" spans="1:15" ht="42" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -2319,10 +2449,11 @@
       <c r="J86" s="4"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
-      <c r="M86" s="5"/>
-      <c r="N86" s="6"/>
-    </row>
-    <row r="87" spans="1:14" ht="42" customHeight="1">
+      <c r="M86" s="4"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="6"/>
+    </row>
+    <row r="87" spans="1:15" ht="42" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -2335,10 +2466,11 @@
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
       <c r="L87" s="4"/>
-      <c r="M87" s="5"/>
-      <c r="N87" s="6"/>
-    </row>
-    <row r="88" spans="1:14" ht="42" customHeight="1">
+      <c r="M87" s="4"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="6"/>
+    </row>
+    <row r="88" spans="1:15" ht="42" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -2351,10 +2483,11 @@
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
-      <c r="M88" s="5"/>
-      <c r="N88" s="6"/>
-    </row>
-    <row r="89" spans="1:14" ht="42" customHeight="1">
+      <c r="M88" s="4"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="6"/>
+    </row>
+    <row r="89" spans="1:15" ht="42" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -2367,10 +2500,11 @@
       <c r="J89" s="4"/>
       <c r="K89" s="4"/>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
-    </row>
-    <row r="90" spans="1:14" ht="42" customHeight="1">
+      <c r="M89" s="4"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="6"/>
+    </row>
+    <row r="90" spans="1:15" ht="42" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -2383,10 +2517,11 @@
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
-    </row>
-    <row r="91" spans="1:14" ht="42" customHeight="1">
+      <c r="M90" s="4"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="6"/>
+    </row>
+    <row r="91" spans="1:15" ht="42" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -2399,10 +2534,11 @@
       <c r="J91" s="4"/>
       <c r="K91" s="4"/>
       <c r="L91" s="4"/>
-      <c r="M91" s="5"/>
-      <c r="N91" s="6"/>
-    </row>
-    <row r="92" spans="1:14" ht="42" customHeight="1">
+      <c r="M91" s="4"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="6"/>
+    </row>
+    <row r="92" spans="1:15" ht="42" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -2415,10 +2551,11 @@
       <c r="J92" s="4"/>
       <c r="K92" s="4"/>
       <c r="L92" s="4"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="6"/>
-    </row>
-    <row r="93" spans="1:14" ht="42" customHeight="1">
+      <c r="M92" s="4"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="6"/>
+    </row>
+    <row r="93" spans="1:15" ht="42" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -2431,10 +2568,11 @@
       <c r="J93" s="4"/>
       <c r="K93" s="4"/>
       <c r="L93" s="4"/>
-      <c r="M93" s="5"/>
-      <c r="N93" s="6"/>
-    </row>
-    <row r="94" spans="1:14" ht="42" customHeight="1">
+      <c r="M93" s="4"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="6"/>
+    </row>
+    <row r="94" spans="1:15" ht="42" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -2447,10 +2585,11 @@
       <c r="J94" s="4"/>
       <c r="K94" s="4"/>
       <c r="L94" s="4"/>
-      <c r="M94" s="5"/>
-      <c r="N94" s="6"/>
-    </row>
-    <row r="95" spans="1:14" ht="42" customHeight="1">
+      <c r="M94" s="4"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="6"/>
+    </row>
+    <row r="95" spans="1:15" ht="42" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -2463,10 +2602,11 @@
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
-      <c r="M95" s="5"/>
-      <c r="N95" s="6"/>
-    </row>
-    <row r="96" spans="1:14" ht="42" customHeight="1">
+      <c r="M95" s="4"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="6"/>
+    </row>
+    <row r="96" spans="1:15" ht="42" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -2479,10 +2619,11 @@
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
-      <c r="M96" s="5"/>
-      <c r="N96" s="6"/>
-    </row>
-    <row r="97" spans="1:14" ht="42" customHeight="1">
+      <c r="M96" s="4"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="6"/>
+    </row>
+    <row r="97" spans="1:15" ht="42" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -2495,10 +2636,11 @@
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
-      <c r="M97" s="5"/>
-      <c r="N97" s="6"/>
-    </row>
-    <row r="98" spans="1:14" ht="42" customHeight="1">
+      <c r="M97" s="4"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="6"/>
+    </row>
+    <row r="98" spans="1:15" ht="42" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -2511,10 +2653,11 @@
       <c r="J98" s="4"/>
       <c r="K98" s="4"/>
       <c r="L98" s="4"/>
-      <c r="M98" s="5"/>
-      <c r="N98" s="6"/>
-    </row>
-    <row r="99" spans="1:14" ht="42" customHeight="1">
+      <c r="M98" s="4"/>
+      <c r="N98" s="5"/>
+      <c r="O98" s="6"/>
+    </row>
+    <row r="99" spans="1:15" ht="42" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -2527,10 +2670,11 @@
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
-      <c r="M99" s="5"/>
-      <c r="N99" s="6"/>
-    </row>
-    <row r="100" spans="1:14" ht="42" customHeight="1">
+      <c r="M99" s="4"/>
+      <c r="N99" s="5"/>
+      <c r="O99" s="6"/>
+    </row>
+    <row r="100" spans="1:15" ht="42" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -2543,10 +2687,11 @@
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="6"/>
-    </row>
-    <row r="101" spans="1:14" ht="42" customHeight="1">
+      <c r="M100" s="4"/>
+      <c r="N100" s="5"/>
+      <c r="O100" s="6"/>
+    </row>
+    <row r="101" spans="1:15" ht="42" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -2559,10 +2704,11 @@
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
-      <c r="M101" s="5"/>
-      <c r="N101" s="6"/>
-    </row>
-    <row r="102" spans="1:14" ht="42" customHeight="1">
+      <c r="M101" s="4"/>
+      <c r="N101" s="5"/>
+      <c r="O101" s="6"/>
+    </row>
+    <row r="102" spans="1:15" ht="42" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -2575,10 +2721,11 @@
       <c r="J102" s="4"/>
       <c r="K102" s="4"/>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-    </row>
-    <row r="103" spans="1:14" ht="42" customHeight="1">
+      <c r="M102" s="4"/>
+      <c r="N102" s="5"/>
+      <c r="O102" s="6"/>
+    </row>
+    <row r="103" spans="1:15" ht="42" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -2591,10 +2738,11 @@
       <c r="J103" s="4"/>
       <c r="K103" s="4"/>
       <c r="L103" s="4"/>
-      <c r="M103" s="5"/>
-      <c r="N103" s="6"/>
-    </row>
-    <row r="104" spans="1:14" ht="42" customHeight="1">
+      <c r="M103" s="4"/>
+      <c r="N103" s="5"/>
+      <c r="O103" s="6"/>
+    </row>
+    <row r="104" spans="1:15" ht="42" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -2607,10 +2755,11 @@
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="6"/>
-    </row>
-    <row r="105" spans="1:14" ht="42" customHeight="1">
+      <c r="M104" s="4"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="6"/>
+    </row>
+    <row r="105" spans="1:15" ht="42" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -2623,10 +2772,11 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="6"/>
-    </row>
-    <row r="106" spans="1:14" ht="42" customHeight="1">
+      <c r="M105" s="4"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="6"/>
+    </row>
+    <row r="106" spans="1:15" ht="42" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -2639,10 +2789,11 @@
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="6"/>
-    </row>
-    <row r="107" spans="1:14" ht="42" customHeight="1">
+      <c r="M106" s="4"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="6"/>
+    </row>
+    <row r="107" spans="1:15" ht="42" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -2655,10 +2806,11 @@
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
-      <c r="M107" s="5"/>
-      <c r="N107" s="6"/>
-    </row>
-    <row r="108" spans="1:14" ht="42" customHeight="1">
+      <c r="M107" s="4"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="6"/>
+    </row>
+    <row r="108" spans="1:15" ht="42" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -2671,10 +2823,11 @@
       <c r="J108" s="4"/>
       <c r="K108" s="4"/>
       <c r="L108" s="4"/>
-      <c r="M108" s="5"/>
-      <c r="N108" s="6"/>
-    </row>
-    <row r="109" spans="1:14" ht="42" customHeight="1">
+      <c r="M108" s="4"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="6"/>
+    </row>
+    <row r="109" spans="1:15" ht="42" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -2687,10 +2840,11 @@
       <c r="J109" s="4"/>
       <c r="K109" s="4"/>
       <c r="L109" s="4"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="6"/>
-    </row>
-    <row r="110" spans="1:14" ht="42" customHeight="1">
+      <c r="M109" s="4"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="6"/>
+    </row>
+    <row r="110" spans="1:15" ht="42" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -2703,10 +2857,11 @@
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="6"/>
-    </row>
-    <row r="111" spans="1:14" ht="42" customHeight="1">
+      <c r="M110" s="4"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="6"/>
+    </row>
+    <row r="111" spans="1:15" ht="42" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -2719,10 +2874,11 @@
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4"/>
-      <c r="M111" s="5"/>
-      <c r="N111" s="6"/>
-    </row>
-    <row r="112" spans="1:14" ht="42" customHeight="1">
+      <c r="M111" s="4"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="6"/>
+    </row>
+    <row r="112" spans="1:15" ht="42" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -2735,10 +2891,11 @@
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4"/>
-      <c r="M112" s="5"/>
-      <c r="N112" s="6"/>
-    </row>
-    <row r="113" spans="1:14" ht="42" customHeight="1">
+      <c r="M112" s="4"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="6"/>
+    </row>
+    <row r="113" spans="1:15" ht="42" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -2751,10 +2908,11 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4"/>
-      <c r="M113" s="5"/>
-      <c r="N113" s="6"/>
-    </row>
-    <row r="114" spans="1:14" ht="42" customHeight="1">
+      <c r="M113" s="4"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="6"/>
+    </row>
+    <row r="114" spans="1:15" ht="42" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -2767,10 +2925,11 @@
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4"/>
-      <c r="M114" s="5"/>
-      <c r="N114" s="6"/>
-    </row>
-    <row r="115" spans="1:14" ht="42" customHeight="1">
+      <c r="M114" s="4"/>
+      <c r="N114" s="5"/>
+      <c r="O114" s="6"/>
+    </row>
+    <row r="115" spans="1:15" ht="42" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -2783,10 +2942,11 @@
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4"/>
-      <c r="M115" s="5"/>
-      <c r="N115" s="6"/>
-    </row>
-    <row r="116" spans="1:14" ht="42" customHeight="1">
+      <c r="M115" s="4"/>
+      <c r="N115" s="5"/>
+      <c r="O115" s="6"/>
+    </row>
+    <row r="116" spans="1:15" ht="42" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -2799,10 +2959,11 @@
       <c r="J116" s="4"/>
       <c r="K116" s="4"/>
       <c r="L116" s="4"/>
-      <c r="M116" s="5"/>
-      <c r="N116" s="6"/>
-    </row>
-    <row r="117" spans="1:14" ht="42" customHeight="1">
+      <c r="M116" s="4"/>
+      <c r="N116" s="5"/>
+      <c r="O116" s="6"/>
+    </row>
+    <row r="117" spans="1:15" ht="42" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -2815,10 +2976,11 @@
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="6"/>
-    </row>
-    <row r="118" spans="1:14" ht="42" customHeight="1">
+      <c r="M117" s="4"/>
+      <c r="N117" s="5"/>
+      <c r="O117" s="6"/>
+    </row>
+    <row r="118" spans="1:15" ht="42" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -2831,10 +2993,11 @@
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="6"/>
-    </row>
-    <row r="119" spans="1:14" ht="42" customHeight="1">
+      <c r="M118" s="4"/>
+      <c r="N118" s="5"/>
+      <c r="O118" s="6"/>
+    </row>
+    <row r="119" spans="1:15" ht="42" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -2847,10 +3010,11 @@
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4"/>
-      <c r="M119" s="5"/>
-      <c r="N119" s="6"/>
-    </row>
-    <row r="120" spans="1:14" ht="42" customHeight="1">
+      <c r="M119" s="4"/>
+      <c r="N119" s="5"/>
+      <c r="O119" s="6"/>
+    </row>
+    <row r="120" spans="1:15" ht="42" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -2863,10 +3027,11 @@
       <c r="J120" s="4"/>
       <c r="K120" s="4"/>
       <c r="L120" s="4"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="6"/>
-    </row>
-    <row r="121" spans="1:14" ht="42" customHeight="1">
+      <c r="M120" s="4"/>
+      <c r="N120" s="5"/>
+      <c r="O120" s="6"/>
+    </row>
+    <row r="121" spans="1:15" ht="42" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -2879,10 +3044,11 @@
       <c r="J121" s="4"/>
       <c r="K121" s="4"/>
       <c r="L121" s="4"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="6"/>
-    </row>
-    <row r="122" spans="1:14" ht="42" customHeight="1">
+      <c r="M121" s="4"/>
+      <c r="N121" s="5"/>
+      <c r="O121" s="6"/>
+    </row>
+    <row r="122" spans="1:15" ht="42" customHeight="1">
       <c r="A122" s="7"/>
       <c r="B122" s="8"/>
       <c r="C122" s="8"/>
@@ -2895,27 +3061,28 @@
       <c r="J122" s="9"/>
       <c r="K122" s="9"/>
       <c r="L122" s="9"/>
-      <c r="M122" s="10"/>
-      <c r="N122" s="11"/>
+      <c r="M122" s="9"/>
+      <c r="N122" s="10"/>
+      <c r="O122" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="K2:K122">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="通过"/>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="失败"/>
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="阻塞"/>
+  <conditionalFormatting sqref="L2:L122">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="通过"/>
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="阻塞"/>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="K2:K122" xr:uid="{353B7FF2-5627-40F5-80B9-0D55ED0B51E0}">
+    <dataValidation type="list" sqref="L2:L122" xr:uid="{353B7FF2-5627-40F5-80B9-0D55ED0B51E0}">
       <formula1>"未执行,通过,失败,阻塞"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J122" xr:uid="{EDC992EC-9ACB-4DE4-9DAC-49537D1BCED1}">
+    <dataValidation type="list" sqref="J2:K122" xr:uid="{EDC992EC-9ACB-4DE4-9DAC-49537D1BCED1}">
       <formula1>"是,否,待确认"</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="I2:I122" xr:uid="{CE3EB946-6813-4DFB-8A6A-5394F18DDE6D}">
       <formula1>"P0,P1,P2"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J5" xr:uid="{E034A03B-2FCE-42FE-BF04-604D33287657}">
+    <dataValidation type="list" sqref="J2:K5" xr:uid="{E034A03B-2FCE-42FE-BF04-604D33287657}">
       <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4986,9 +5153,9 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="K2:K120">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="通过"/>
-    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="失败"/>
-    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="阻塞"/>
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="通过"/>
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="失败"/>
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="阻塞"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" sqref="J2:J5" xr:uid="{E7526064-7012-45D0-9069-94EBB7B82F2C}">

--- a/tests/Common_Test_Cases/建设项目_个性化用例.xlsx
+++ b/tests/Common_Test_Cases/建设项目_个性化用例.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Auto_Testing\UI-Smoke-Testing\tests\Common_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D067B59-F651-4BD3-B587-0DE2C092C977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907944BC-4AB1-49FA-AEB8-59221E1E44D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="新增项目" sheetId="1" r:id="rId1"/>
     <sheet name="项目决策" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="建设项目" sheetId="3" r:id="rId3"/>
+    <sheet name="项目进度" sheetId="5" r:id="rId4"/>
+    <sheet name="项目运行信息" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="79">
   <si>
     <t>用例ID</t>
   </si>
@@ -225,6 +227,87 @@
     <t>自动化执行方式</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>编辑</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>建设项目</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>建设项目不可修改</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>JS-EDIT-001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>已登录且有项目进度编辑权限；已打开一条可编辑项目进度记录的编辑表单</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>记录当前“建设项目”展示值</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>试点击、输入、选择或清空“建设项目”；再执行保存</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>建设项目控件为只读或禁用，无法修改；尝试操作后值保持不变；保存请求中的建设项目 ID/名称与编辑前一致</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>JS-ADD-001</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增按钮</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增操作拦截校验 - 满足条件可新增</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新增操作拦截校验 - 不满足条件拦截</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目状态：项目决策</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>项目状态：非项目决策</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>非项目决策的项目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>已项目决策的项目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 进入项目进度页面
+2. 点击【新增】按钮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>弹出提示：项目未完成决策，不允许新增项目进度；无法打开新增弹窗</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功打开新增项目进度弹窗，可正常录入数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JS-ADD-002</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -233,7 +316,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,6 +350,12 @@
       <sz val="9"/>
       <name val="宋体"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -444,42 +533,37 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="19">
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color rgb="FF1F2937"/>
-        <name val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-        <scheme val="none"/>
+        <color rgb="FF7F6000"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFE5E7EB"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFE5E7EB"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD9E2F3"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD9E2F3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -543,6 +627,135 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7F6000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FFC00000"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF375623"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2F0D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color rgb="FF1F2937"/>
+        <name val="Microsoft YaHei"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFE5E7EB"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFE5E7EB"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFD9E2F3"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFD9E2F3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -570,7 +783,7 @@
     <tableColumn id="8" xr3:uid="{6512512F-DD54-4049-87F4-E7C213779827}" name="预期结果"/>
     <tableColumn id="9" xr3:uid="{934FFC46-C527-48F3-92DE-A699B77142B5}" name="优先级"/>
     <tableColumn id="10" xr3:uid="{1A5D63AF-4864-467E-AF6F-302AE1D22C24}" name="是否自动化"/>
-    <tableColumn id="15" xr3:uid="{7F9C8BE8-00E0-4E4E-B870-27935BC02D6F}" name="自动化执行方式" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{7F9C8BE8-00E0-4E4E-B870-27935BC02D6F}" name="自动化执行方式" dataDxfId="18"/>
     <tableColumn id="11" xr3:uid="{CB104130-AC1C-4391-8144-79CB45D4EAA4}" name="执行结果"/>
     <tableColumn id="12" xr3:uid="{2C556962-D51B-43AE-B4E4-97C77DC2AFC7}" name="测试人员"/>
     <tableColumn id="13" xr3:uid="{64E9F646-5326-4C9D-92BA-25BABA77BDCC}" name="测试日期"/>
@@ -598,6 +811,75 @@
     <tableColumn id="12" xr3:uid="{695F25DA-BD6B-452B-917B-936467835E27}" name="测试人员"/>
     <tableColumn id="13" xr3:uid="{E6BB0054-21D3-4322-819C-32A20967B70B}" name="测试日期"/>
     <tableColumn id="14" xr3:uid="{5EBA1033-53EC-45C6-B5AB-CCE5C6DDBA00}" name="备注"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{66B942F7-F40F-460D-B29F-302123B4935E}" name="OptimizedAddCases34" displayName="OptimizedAddCases34" ref="A1:N120" totalsRowShown="0">
+  <autoFilter ref="A1:N120" xr:uid="{66B942F7-F40F-460D-B29F-302123B4935E}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{A3B9A230-F03D-49EB-91B0-C1835FC9E0D8}" name="用例ID"/>
+    <tableColumn id="2" xr3:uid="{F9DA4513-22E2-49D1-B5AC-7B93EC257E5D}" name="功能"/>
+    <tableColumn id="3" xr3:uid="{A94E911B-9ECE-41BE-8290-98B63871E621}" name="字段/控件"/>
+    <tableColumn id="4" xr3:uid="{7A70896B-09F7-41FA-A5E5-6EDC35008C6B}" name="测试场景"/>
+    <tableColumn id="5" xr3:uid="{2A6BBFFE-D769-459B-A2D0-2218FB8CC9D5}" name="前置条件"/>
+    <tableColumn id="6" xr3:uid="{D8FF5576-F263-4722-9DF4-DE3CCB4DE6E7}" name="测试数据"/>
+    <tableColumn id="7" xr3:uid="{357C99E6-2AC7-45FA-A415-C89E607E6517}" name="操作步骤"/>
+    <tableColumn id="8" xr3:uid="{0EE5E4EC-84EB-4198-AEB3-67D950EDD513}" name="预期结果"/>
+    <tableColumn id="9" xr3:uid="{EF7C9BD9-5C64-4010-9768-2D1917C47424}" name="优先级"/>
+    <tableColumn id="10" xr3:uid="{D73E2BF2-E3D0-4DCE-B40B-1D5389035378}" name="是否自动化"/>
+    <tableColumn id="11" xr3:uid="{2866EC5A-2C8C-46E3-AF6C-BD276CFD4873}" name="执行结果"/>
+    <tableColumn id="12" xr3:uid="{82FD2E40-D707-4B01-8776-190051F3805B}" name="测试人员"/>
+    <tableColumn id="13" xr3:uid="{3FEB84E5-C4E7-41E5-9253-A4CF551EC01A}" name="测试日期"/>
+    <tableColumn id="14" xr3:uid="{E768E647-6F8C-46DE-AB0B-D21DA0B81F4A}" name="备注"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{86EE11F5-646A-4110-BADC-B0509A632B7B}" name="OptimizedAddCases345" displayName="OptimizedAddCases345" ref="A1:N120" totalsRowShown="0">
+  <autoFilter ref="A1:N120" xr:uid="{66B942F7-F40F-460D-B29F-302123B4935E}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{62915D86-83F1-4D7B-B9FC-33B7F1932358}" name="用例ID"/>
+    <tableColumn id="2" xr3:uid="{D2111961-C3E9-49EB-9486-B995FEEECBFD}" name="功能"/>
+    <tableColumn id="3" xr3:uid="{94AABC0E-B1C3-46DB-A2EC-A477A318804E}" name="字段/控件"/>
+    <tableColumn id="4" xr3:uid="{385D0B53-7789-4E9E-BD8E-B99EE2FDDB48}" name="测试场景"/>
+    <tableColumn id="5" xr3:uid="{25763175-A7EC-4776-BED2-AEBEA7DEF0CC}" name="前置条件"/>
+    <tableColumn id="6" xr3:uid="{A18FD136-7C4F-409B-9D84-967179FB9C1A}" name="测试数据"/>
+    <tableColumn id="7" xr3:uid="{F359A6EE-9E01-4DF3-A4AC-703DB323A1F6}" name="操作步骤"/>
+    <tableColumn id="8" xr3:uid="{0FD39B41-A916-4878-AC68-E1DBE7357F68}" name="预期结果"/>
+    <tableColumn id="9" xr3:uid="{A90AA782-957E-4D78-82E3-BC628D38AFE9}" name="优先级"/>
+    <tableColumn id="10" xr3:uid="{E7561DEA-2C1C-45DB-B986-7B74671057F6}" name="是否自动化"/>
+    <tableColumn id="11" xr3:uid="{6324EF36-B588-49EE-B08A-6E15AA1D0D72}" name="执行结果"/>
+    <tableColumn id="12" xr3:uid="{69DDCFFF-3C46-4370-9569-3F59D1AD97B4}" name="测试人员"/>
+    <tableColumn id="13" xr3:uid="{F38D48B4-DDC3-4FD2-A1D2-4F8437182CB0}" name="测试日期"/>
+    <tableColumn id="14" xr3:uid="{B5212D8B-B002-4F7D-B577-87C6448B7446}" name="备注"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4518E147-FD0F-48E0-96A6-FB3A28D7407D}" name="OptimizedAddCases3456" displayName="OptimizedAddCases3456" ref="A1:N120" totalsRowShown="0">
+  <autoFilter ref="A1:N120" xr:uid="{66B942F7-F40F-460D-B29F-302123B4935E}"/>
+  <tableColumns count="14">
+    <tableColumn id="1" xr3:uid="{02F4C4D2-33ED-4543-B355-99D03467BFA2}" name="用例ID"/>
+    <tableColumn id="2" xr3:uid="{B5BD045A-EA7E-47EE-9A0D-3F75E6FD4E6F}" name="功能"/>
+    <tableColumn id="3" xr3:uid="{F45CC856-650A-4CA1-801B-9D1D7C14D77A}" name="字段/控件"/>
+    <tableColumn id="4" xr3:uid="{9E52FD2C-48AB-4402-86D5-3A5010329F26}" name="测试场景"/>
+    <tableColumn id="5" xr3:uid="{E5931C39-CAD8-4FFA-A1BE-22BF1B184E60}" name="前置条件"/>
+    <tableColumn id="6" xr3:uid="{A526700C-54DE-46FC-988A-9850D39396F2}" name="测试数据"/>
+    <tableColumn id="7" xr3:uid="{81AD972C-BCF4-46F8-907F-1D0259C89B34}" name="操作步骤"/>
+    <tableColumn id="8" xr3:uid="{158A8BA2-58E9-46BA-BACE-8AC21418FA31}" name="预期结果"/>
+    <tableColumn id="9" xr3:uid="{6BCB53D4-F68D-47A8-8A27-7D460561163A}" name="优先级"/>
+    <tableColumn id="10" xr3:uid="{674125B4-EAA1-4962-9BD3-A68225121816}" name="是否自动化"/>
+    <tableColumn id="11" xr3:uid="{F03A582E-7DE0-4484-9370-EF7709975844}" name="执行结果"/>
+    <tableColumn id="12" xr3:uid="{B969E3E9-5398-4F7F-B2EF-356D02203FBC}" name="测试人员"/>
+    <tableColumn id="13" xr3:uid="{32AC5F25-4CBB-40DA-B961-33804D4FAFFF}" name="测试日期"/>
+    <tableColumn id="14" xr3:uid="{6802DCA7-97EA-411F-A13F-6BE3E6EBA4B3}" name="备注"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3068,9 +3350,9 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="L2:L122">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="通过"/>
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="失败"/>
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="阻塞"/>
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="通过"/>
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="失败"/>
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="阻塞"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" sqref="L2:L122" xr:uid="{353B7FF2-5627-40F5-80B9-0D55ED0B51E0}">
@@ -5153,9 +5435,9 @@
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="K2:K120">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="通过"/>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="失败"/>
-    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="阻塞"/>
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="通过"/>
+    <cfRule type="containsText" dxfId="10" priority="5" operator="containsText" text="失败"/>
+    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="阻塞"/>
   </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation type="list" sqref="J2:J5" xr:uid="{E7526064-7012-45D0-9069-94EBB7B82F2C}">
@@ -5181,11 +5463,6071 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:N120"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="42" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="42" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" ht="42" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="42" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" ht="42" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="42" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" ht="42" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="42" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" ht="42" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="42" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" ht="42" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="42" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="42" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="42" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="42" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="42" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="42" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" ht="42" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="42" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" ht="42" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" ht="42" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" ht="42" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" ht="42" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" ht="42" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" ht="42" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" ht="42" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" ht="42" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" ht="42" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14" ht="42" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:14" ht="42" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:14" ht="42" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="1:14" ht="42" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" ht="42" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" ht="42" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" ht="42" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" ht="42" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14" ht="42" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" spans="1:14" ht="42" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="1:14" ht="42" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" spans="1:14" ht="42" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" spans="1:14" ht="42" customHeight="1">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="1:14" ht="42" customHeight="1">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:14" ht="42" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" spans="1:14" ht="42" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="6"/>
+    </row>
+    <row r="46" spans="1:14" ht="42" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="6"/>
+    </row>
+    <row r="47" spans="1:14" ht="42" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6"/>
+    </row>
+    <row r="48" spans="1:14" ht="42" customHeight="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="6"/>
+    </row>
+    <row r="49" spans="1:14" ht="42" customHeight="1">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="6"/>
+    </row>
+    <row r="50" spans="1:14" ht="42" customHeight="1">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="6"/>
+    </row>
+    <row r="51" spans="1:14" ht="42" customHeight="1">
+      <c r="A51" s="2"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="6"/>
+    </row>
+    <row r="52" spans="1:14" ht="42" customHeight="1">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" spans="1:14" ht="42" customHeight="1">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" spans="1:14" ht="42" customHeight="1">
+      <c r="A54" s="2"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="6"/>
+    </row>
+    <row r="55" spans="1:14" ht="42" customHeight="1">
+      <c r="A55" s="2"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" spans="1:14" ht="42" customHeight="1">
+      <c r="A56" s="2"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57" spans="1:14" ht="42" customHeight="1">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" spans="1:14" ht="42" customHeight="1">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="6"/>
+    </row>
+    <row r="59" spans="1:14" ht="42" customHeight="1">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="6"/>
+    </row>
+    <row r="60" spans="1:14" ht="42" customHeight="1">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61" spans="1:14" ht="42" customHeight="1">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" spans="1:14" ht="42" customHeight="1">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="6"/>
+    </row>
+    <row r="63" spans="1:14" ht="42" customHeight="1">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="6"/>
+    </row>
+    <row r="64" spans="1:14" ht="42" customHeight="1">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" spans="1:14" ht="42" customHeight="1">
+      <c r="A65" s="2"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" spans="1:14" ht="42" customHeight="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" spans="1:14" ht="42" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="6"/>
+    </row>
+    <row r="68" spans="1:14" ht="42" customHeight="1">
+      <c r="A68" s="2"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:14" ht="42" customHeight="1">
+      <c r="A69" s="2"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" ht="42" customHeight="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="1:14" ht="42" customHeight="1">
+      <c r="A71" s="2"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="1:14" ht="42" customHeight="1">
+      <c r="A72" s="2"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="1:14" ht="42" customHeight="1">
+      <c r="A73" s="2"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="1:14" ht="42" customHeight="1">
+      <c r="A74" s="2"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="1:14" ht="42" customHeight="1">
+      <c r="A75" s="2"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="1:14" ht="42" customHeight="1">
+      <c r="A76" s="2"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="1:14" ht="42" customHeight="1">
+      <c r="A77" s="2"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" spans="1:14" ht="42" customHeight="1">
+      <c r="A78" s="2"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" spans="1:14" ht="42" customHeight="1">
+      <c r="A79" s="2"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" spans="1:14" ht="42" customHeight="1">
+      <c r="A80" s="2"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" spans="1:14" ht="42" customHeight="1">
+      <c r="A81" s="2"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="1:14" ht="42" customHeight="1">
+      <c r="A82" s="2"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" spans="1:14" ht="42" customHeight="1">
+      <c r="A83" s="2"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" spans="1:14" ht="42" customHeight="1">
+      <c r="A84" s="2"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" spans="1:14" ht="42" customHeight="1">
+      <c r="A85" s="2"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" spans="1:14" ht="42" customHeight="1">
+      <c r="A86" s="2"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" spans="1:14" ht="42" customHeight="1">
+      <c r="A87" s="2"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" spans="1:14" ht="42" customHeight="1">
+      <c r="A88" s="2"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" spans="1:14" ht="42" customHeight="1">
+      <c r="A89" s="2"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" spans="1:14" ht="42" customHeight="1">
+      <c r="A90" s="2"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" spans="1:14" ht="42" customHeight="1">
+      <c r="A91" s="2"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" spans="1:14" ht="42" customHeight="1">
+      <c r="A92" s="2"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" spans="1:14" ht="42" customHeight="1">
+      <c r="A93" s="2"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="1:14" ht="42" customHeight="1">
+      <c r="A94" s="2"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" spans="1:14" ht="42" customHeight="1">
+      <c r="A95" s="2"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" spans="1:14" ht="42" customHeight="1">
+      <c r="A96" s="2"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" spans="1:14" ht="42" customHeight="1">
+      <c r="A97" s="2"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" spans="1:14" ht="42" customHeight="1">
+      <c r="A98" s="2"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="1:14" ht="42" customHeight="1">
+      <c r="A99" s="2"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" spans="1:14" ht="42" customHeight="1">
+      <c r="A100" s="2"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="1:14" ht="42" customHeight="1">
+      <c r="A101" s="2"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" ht="42" customHeight="1">
+      <c r="A102" s="2"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" ht="42" customHeight="1">
+      <c r="A103" s="2"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="1:14" ht="42" customHeight="1">
+      <c r="A104" s="2"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="1:14" ht="42" customHeight="1">
+      <c r="A105" s="2"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" ht="42" customHeight="1">
+      <c r="A106" s="2"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="1:14" ht="42" customHeight="1">
+      <c r="A107" s="2"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" ht="42" customHeight="1">
+      <c r="A108" s="2"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="1:14" ht="42" customHeight="1">
+      <c r="A109" s="2"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="1:14" ht="42" customHeight="1">
+      <c r="A110" s="2"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" ht="42" customHeight="1">
+      <c r="A111" s="2"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:14" ht="42" customHeight="1">
+      <c r="A112" s="2"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:14" ht="42" customHeight="1">
+      <c r="A113" s="2"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:14" ht="42" customHeight="1">
+      <c r="A114" s="2"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="1:14" ht="42" customHeight="1">
+      <c r="A115" s="2"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" ht="42" customHeight="1">
+      <c r="A116" s="2"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="5"/>
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="1:14" ht="42" customHeight="1">
+      <c r="A117" s="2"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="1:14" ht="42" customHeight="1">
+      <c r="A118" s="2"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="1:14" ht="42" customHeight="1">
+      <c r="A119" s="2"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="1:14" ht="42" customHeight="1">
+      <c r="A120" s="7"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9"/>
+      <c r="L120" s="9"/>
+      <c r="M120" s="10"/>
+      <c r="N120" s="11"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="K2:K120">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="通过"/>
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="失败"/>
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="阻塞"/>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="K2:K120" xr:uid="{4F02C9CB-FAF7-4319-B34E-DF76E7723BC7}">
+      <formula1>"未执行,通过,失败,阻塞"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J2:J120" xr:uid="{F173926D-A4AB-4807-8B55-9545A8C26BBA}">
+      <formula1>"是,否,待确认"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I2:I120" xr:uid="{32125922-571B-4DCF-BDC3-7F9221C0242A}">
+      <formula1>"P0,P1,P2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J2:J5" xr:uid="{79B4A9CE-F728-4311-AAFC-E5BF1233EC3B}">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE5886B4-36C9-45E0-A0EC-2431C7EF2858}">
+  <dimension ref="A1:N120"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="42" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="42" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" ht="42" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="42" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" ht="42" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="42" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" ht="42" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="42" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" ht="42" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="42" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" ht="42" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="42" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="42" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="42" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="42" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="42" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="42" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" ht="42" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="42" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" ht="42" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" ht="42" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" ht="42" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" ht="42" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" ht="42" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" ht="42" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" ht="42" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" ht="42" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" ht="42" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14" ht="42" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:14" ht="42" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:14" ht="42" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="1:14" ht="42" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" ht="42" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" ht="42" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" ht="42" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" ht="42" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14" ht="42" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" spans="1:14" ht="42" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="1:14" ht="42" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" spans="1:14" ht="42" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" spans="1:14" ht="42" customHeight="1">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="1:14" ht="42" customHeight="1">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:14" ht="42" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" spans="1:14" ht="42" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="6"/>
+    </row>
+    <row r="46" spans="1:14" ht="42" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="6"/>
+    </row>
+    <row r="47" spans="1:14" ht="42" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6"/>
+    </row>
+    <row r="48" spans="1:14" ht="42" customHeight="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="6"/>
+    </row>
+    <row r="49" spans="1:14" ht="42" customHeight="1">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="6"/>
+    </row>
+    <row r="50" spans="1:14" ht="42" customHeight="1">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="6"/>
+    </row>
+    <row r="51" spans="1:14" ht="42" customHeight="1">
+      <c r="A51" s="2"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="6"/>
+    </row>
+    <row r="52" spans="1:14" ht="42" customHeight="1">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" spans="1:14" ht="42" customHeight="1">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" spans="1:14" ht="42" customHeight="1">
+      <c r="A54" s="2"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="6"/>
+    </row>
+    <row r="55" spans="1:14" ht="42" customHeight="1">
+      <c r="A55" s="2"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" spans="1:14" ht="42" customHeight="1">
+      <c r="A56" s="2"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57" spans="1:14" ht="42" customHeight="1">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" spans="1:14" ht="42" customHeight="1">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="6"/>
+    </row>
+    <row r="59" spans="1:14" ht="42" customHeight="1">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="6"/>
+    </row>
+    <row r="60" spans="1:14" ht="42" customHeight="1">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61" spans="1:14" ht="42" customHeight="1">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" spans="1:14" ht="42" customHeight="1">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="6"/>
+    </row>
+    <row r="63" spans="1:14" ht="42" customHeight="1">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="6"/>
+    </row>
+    <row r="64" spans="1:14" ht="42" customHeight="1">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" spans="1:14" ht="42" customHeight="1">
+      <c r="A65" s="2"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" spans="1:14" ht="42" customHeight="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" spans="1:14" ht="42" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="6"/>
+    </row>
+    <row r="68" spans="1:14" ht="42" customHeight="1">
+      <c r="A68" s="2"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:14" ht="42" customHeight="1">
+      <c r="A69" s="2"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" ht="42" customHeight="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="1:14" ht="42" customHeight="1">
+      <c r="A71" s="2"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="1:14" ht="42" customHeight="1">
+      <c r="A72" s="2"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="1:14" ht="42" customHeight="1">
+      <c r="A73" s="2"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="1:14" ht="42" customHeight="1">
+      <c r="A74" s="2"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="1:14" ht="42" customHeight="1">
+      <c r="A75" s="2"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="1:14" ht="42" customHeight="1">
+      <c r="A76" s="2"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="1:14" ht="42" customHeight="1">
+      <c r="A77" s="2"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" spans="1:14" ht="42" customHeight="1">
+      <c r="A78" s="2"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" spans="1:14" ht="42" customHeight="1">
+      <c r="A79" s="2"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" spans="1:14" ht="42" customHeight="1">
+      <c r="A80" s="2"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" spans="1:14" ht="42" customHeight="1">
+      <c r="A81" s="2"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="1:14" ht="42" customHeight="1">
+      <c r="A82" s="2"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" spans="1:14" ht="42" customHeight="1">
+      <c r="A83" s="2"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" spans="1:14" ht="42" customHeight="1">
+      <c r="A84" s="2"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" spans="1:14" ht="42" customHeight="1">
+      <c r="A85" s="2"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" spans="1:14" ht="42" customHeight="1">
+      <c r="A86" s="2"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" spans="1:14" ht="42" customHeight="1">
+      <c r="A87" s="2"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" spans="1:14" ht="42" customHeight="1">
+      <c r="A88" s="2"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" spans="1:14" ht="42" customHeight="1">
+      <c r="A89" s="2"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" spans="1:14" ht="42" customHeight="1">
+      <c r="A90" s="2"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" spans="1:14" ht="42" customHeight="1">
+      <c r="A91" s="2"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" spans="1:14" ht="42" customHeight="1">
+      <c r="A92" s="2"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" spans="1:14" ht="42" customHeight="1">
+      <c r="A93" s="2"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="1:14" ht="42" customHeight="1">
+      <c r="A94" s="2"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" spans="1:14" ht="42" customHeight="1">
+      <c r="A95" s="2"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" spans="1:14" ht="42" customHeight="1">
+      <c r="A96" s="2"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" spans="1:14" ht="42" customHeight="1">
+      <c r="A97" s="2"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" spans="1:14" ht="42" customHeight="1">
+      <c r="A98" s="2"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="1:14" ht="42" customHeight="1">
+      <c r="A99" s="2"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" spans="1:14" ht="42" customHeight="1">
+      <c r="A100" s="2"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="1:14" ht="42" customHeight="1">
+      <c r="A101" s="2"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" ht="42" customHeight="1">
+      <c r="A102" s="2"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" ht="42" customHeight="1">
+      <c r="A103" s="2"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="1:14" ht="42" customHeight="1">
+      <c r="A104" s="2"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="1:14" ht="42" customHeight="1">
+      <c r="A105" s="2"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" ht="42" customHeight="1">
+      <c r="A106" s="2"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="1:14" ht="42" customHeight="1">
+      <c r="A107" s="2"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" ht="42" customHeight="1">
+      <c r="A108" s="2"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="1:14" ht="42" customHeight="1">
+      <c r="A109" s="2"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="1:14" ht="42" customHeight="1">
+      <c r="A110" s="2"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" ht="42" customHeight="1">
+      <c r="A111" s="2"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:14" ht="42" customHeight="1">
+      <c r="A112" s="2"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:14" ht="42" customHeight="1">
+      <c r="A113" s="2"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:14" ht="42" customHeight="1">
+      <c r="A114" s="2"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="1:14" ht="42" customHeight="1">
+      <c r="A115" s="2"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" ht="42" customHeight="1">
+      <c r="A116" s="2"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="5"/>
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="1:14" ht="42" customHeight="1">
+      <c r="A117" s="2"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="1:14" ht="42" customHeight="1">
+      <c r="A118" s="2"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="1:14" ht="42" customHeight="1">
+      <c r="A119" s="2"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="1:14" ht="42" customHeight="1">
+      <c r="A120" s="7"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9"/>
+      <c r="L120" s="9"/>
+      <c r="M120" s="10"/>
+      <c r="N120" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="K2:K120">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="通过"/>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="失败"/>
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="阻塞"/>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="J4:J5 J2:J3" xr:uid="{BF9C6B3F-E935-4145-BA44-0F08F7EF397E}">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I4:I120 I2:I3" xr:uid="{7CC40CD8-76C1-4535-B9BB-84C25C953E4A}">
+      <formula1>"P0,P1,P2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J4:J120 J2:J3" xr:uid="{E7483864-E341-42FB-B49B-2925C7C56F88}">
+      <formula1>"是,否,待确认"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K4:K120 K2:K3" xr:uid="{4CE7DF73-7721-4B6E-B3D6-1C3ECDE18D67}">
+      <formula1>"未执行,通过,失败,阻塞"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C284C86-BCEC-432F-9A88-E62F6F5EBC8E}">
+  <dimension ref="A1:N120"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="42" customWidth="1"/>
+    <col min="8" max="8" width="46" customWidth="1"/>
+    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="10" max="11" width="11" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="30" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="42" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" ht="42" customHeight="1">
+      <c r="A3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" ht="42" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="42" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" ht="42" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="42" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="5"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" ht="42" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="42" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="5"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" ht="42" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="5"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" ht="42" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="5"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" ht="42" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="5"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" ht="42" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="5"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="42" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="5"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="42" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="42" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="5"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" ht="42" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="5"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="42" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="5"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" ht="42" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="42" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" ht="42" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" ht="42" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" ht="42" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" ht="42" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" ht="42" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" ht="42" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" ht="42" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" ht="42" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" ht="42" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="6"/>
+    </row>
+    <row r="30" spans="1:14" ht="42" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="3"/>
+      <c r="E30" s="3"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="4"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="6"/>
+    </row>
+    <row r="31" spans="1:14" ht="42" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="4"/>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="5"/>
+      <c r="N31" s="6"/>
+    </row>
+    <row r="32" spans="1:14" ht="42" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="4"/>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="6"/>
+    </row>
+    <row r="33" spans="1:14" ht="42" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="4"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="5"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" ht="42" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="4"/>
+      <c r="J34" s="4"/>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" ht="42" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" ht="42" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="4"/>
+      <c r="J36" s="4"/>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" ht="42" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="6"/>
+    </row>
+    <row r="38" spans="1:14" ht="42" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="4"/>
+      <c r="J38" s="4"/>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="6"/>
+    </row>
+    <row r="39" spans="1:14" ht="42" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="3"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="4"/>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="1:14" ht="42" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="4"/>
+      <c r="J40" s="4"/>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="6"/>
+    </row>
+    <row r="41" spans="1:14" ht="42" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="4"/>
+      <c r="J41" s="4"/>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="6"/>
+    </row>
+    <row r="42" spans="1:14" ht="42" customHeight="1">
+      <c r="A42" s="2"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="4"/>
+      <c r="J42" s="4"/>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="6"/>
+    </row>
+    <row r="43" spans="1:14" ht="42" customHeight="1">
+      <c r="A43" s="2"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="3"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="4"/>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="6"/>
+    </row>
+    <row r="44" spans="1:14" ht="42" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="6"/>
+    </row>
+    <row r="45" spans="1:14" ht="42" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="4"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="6"/>
+    </row>
+    <row r="46" spans="1:14" ht="42" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="4"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="6"/>
+    </row>
+    <row r="47" spans="1:14" ht="42" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="6"/>
+    </row>
+    <row r="48" spans="1:14" ht="42" customHeight="1">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="6"/>
+    </row>
+    <row r="49" spans="1:14" ht="42" customHeight="1">
+      <c r="A49" s="2"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="6"/>
+    </row>
+    <row r="50" spans="1:14" ht="42" customHeight="1">
+      <c r="A50" s="2"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="6"/>
+    </row>
+    <row r="51" spans="1:14" ht="42" customHeight="1">
+      <c r="A51" s="2"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="D51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="6"/>
+    </row>
+    <row r="52" spans="1:14" ht="42" customHeight="1">
+      <c r="A52" s="2"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+      <c r="D52" s="3"/>
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3"/>
+      <c r="H52" s="3"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" spans="1:14" ht="42" customHeight="1">
+      <c r="A53" s="2"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="D53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" spans="1:14" ht="42" customHeight="1">
+      <c r="A54" s="2"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+      <c r="D54" s="3"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="6"/>
+    </row>
+    <row r="55" spans="1:14" ht="42" customHeight="1">
+      <c r="A55" s="2"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="D55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" spans="1:14" ht="42" customHeight="1">
+      <c r="A56" s="2"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57" spans="1:14" ht="42" customHeight="1">
+      <c r="A57" s="2"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="D57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="3"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" spans="1:14" ht="42" customHeight="1">
+      <c r="A58" s="2"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="6"/>
+    </row>
+    <row r="59" spans="1:14" ht="42" customHeight="1">
+      <c r="A59" s="2"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+      <c r="D59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
+      <c r="H59" s="3"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="6"/>
+    </row>
+    <row r="60" spans="1:14" ht="42" customHeight="1">
+      <c r="A60" s="2"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
+      <c r="H60" s="3"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="6"/>
+    </row>
+    <row r="61" spans="1:14" ht="42" customHeight="1">
+      <c r="A61" s="2"/>
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="6"/>
+    </row>
+    <row r="62" spans="1:14" ht="42" customHeight="1">
+      <c r="A62" s="2"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
+      <c r="E62" s="3"/>
+      <c r="F62" s="3"/>
+      <c r="G62" s="3"/>
+      <c r="H62" s="3"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="6"/>
+    </row>
+    <row r="63" spans="1:14" ht="42" customHeight="1">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3"/>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
+      <c r="H63" s="3"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="6"/>
+    </row>
+    <row r="64" spans="1:14" ht="42" customHeight="1">
+      <c r="A64" s="2"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
+      <c r="H64" s="3"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="6"/>
+    </row>
+    <row r="65" spans="1:14" ht="42" customHeight="1">
+      <c r="A65" s="2"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
+      <c r="E65" s="3"/>
+      <c r="F65" s="3"/>
+      <c r="G65" s="3"/>
+      <c r="H65" s="3"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="6"/>
+    </row>
+    <row r="66" spans="1:14" ht="42" customHeight="1">
+      <c r="A66" s="2"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="6"/>
+    </row>
+    <row r="67" spans="1:14" ht="42" customHeight="1">
+      <c r="A67" s="2"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
+      <c r="H67" s="3"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="6"/>
+    </row>
+    <row r="68" spans="1:14" ht="42" customHeight="1">
+      <c r="A68" s="2"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="3"/>
+      <c r="F68" s="3"/>
+      <c r="G68" s="3"/>
+      <c r="H68" s="3"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="6"/>
+    </row>
+    <row r="69" spans="1:14" ht="42" customHeight="1">
+      <c r="A69" s="2"/>
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3"/>
+      <c r="E69" s="3"/>
+      <c r="F69" s="3"/>
+      <c r="G69" s="3"/>
+      <c r="H69" s="3"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="6"/>
+    </row>
+    <row r="70" spans="1:14" ht="42" customHeight="1">
+      <c r="A70" s="2"/>
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="3"/>
+      <c r="F70" s="3"/>
+      <c r="G70" s="3"/>
+      <c r="H70" s="3"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="6"/>
+    </row>
+    <row r="71" spans="1:14" ht="42" customHeight="1">
+      <c r="A71" s="2"/>
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3"/>
+      <c r="E71" s="3"/>
+      <c r="F71" s="3"/>
+      <c r="G71" s="3"/>
+      <c r="H71" s="3"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="6"/>
+    </row>
+    <row r="72" spans="1:14" ht="42" customHeight="1">
+      <c r="A72" s="2"/>
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="3"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="6"/>
+    </row>
+    <row r="73" spans="1:14" ht="42" customHeight="1">
+      <c r="A73" s="2"/>
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="4"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="4"/>
+      <c r="L73" s="4"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="6"/>
+    </row>
+    <row r="74" spans="1:14" ht="42" customHeight="1">
+      <c r="A74" s="2"/>
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="3"/>
+      <c r="F74" s="3"/>
+      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="4"/>
+      <c r="J74" s="4"/>
+      <c r="K74" s="4"/>
+      <c r="L74" s="4"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="6"/>
+    </row>
+    <row r="75" spans="1:14" ht="42" customHeight="1">
+      <c r="A75" s="2"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="6"/>
+    </row>
+    <row r="76" spans="1:14" ht="42" customHeight="1">
+      <c r="A76" s="2"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="6"/>
+    </row>
+    <row r="77" spans="1:14" ht="42" customHeight="1">
+      <c r="A77" s="2"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="6"/>
+    </row>
+    <row r="78" spans="1:14" ht="42" customHeight="1">
+      <c r="A78" s="2"/>
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="6"/>
+    </row>
+    <row r="79" spans="1:14" ht="42" customHeight="1">
+      <c r="A79" s="2"/>
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="4"/>
+      <c r="J79" s="4"/>
+      <c r="K79" s="4"/>
+      <c r="L79" s="4"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="6"/>
+    </row>
+    <row r="80" spans="1:14" ht="42" customHeight="1">
+      <c r="A80" s="2"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="4"/>
+      <c r="J80" s="4"/>
+      <c r="K80" s="4"/>
+      <c r="L80" s="4"/>
+      <c r="M80" s="5"/>
+      <c r="N80" s="6"/>
+    </row>
+    <row r="81" spans="1:14" ht="42" customHeight="1">
+      <c r="A81" s="2"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="4"/>
+      <c r="J81" s="4"/>
+      <c r="K81" s="4"/>
+      <c r="L81" s="4"/>
+      <c r="M81" s="5"/>
+      <c r="N81" s="6"/>
+    </row>
+    <row r="82" spans="1:14" ht="42" customHeight="1">
+      <c r="A82" s="2"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="4"/>
+      <c r="J82" s="4"/>
+      <c r="K82" s="4"/>
+      <c r="L82" s="4"/>
+      <c r="M82" s="5"/>
+      <c r="N82" s="6"/>
+    </row>
+    <row r="83" spans="1:14" ht="42" customHeight="1">
+      <c r="A83" s="2"/>
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="4"/>
+      <c r="J83" s="4"/>
+      <c r="K83" s="4"/>
+      <c r="L83" s="4"/>
+      <c r="M83" s="5"/>
+      <c r="N83" s="6"/>
+    </row>
+    <row r="84" spans="1:14" ht="42" customHeight="1">
+      <c r="A84" s="2"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="4"/>
+      <c r="J84" s="4"/>
+      <c r="K84" s="4"/>
+      <c r="L84" s="4"/>
+      <c r="M84" s="5"/>
+      <c r="N84" s="6"/>
+    </row>
+    <row r="85" spans="1:14" ht="42" customHeight="1">
+      <c r="A85" s="2"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3"/>
+      <c r="E85" s="3"/>
+      <c r="F85" s="3"/>
+      <c r="G85" s="3"/>
+      <c r="H85" s="3"/>
+      <c r="I85" s="4"/>
+      <c r="J85" s="4"/>
+      <c r="K85" s="4"/>
+      <c r="L85" s="4"/>
+      <c r="M85" s="5"/>
+      <c r="N85" s="6"/>
+    </row>
+    <row r="86" spans="1:14" ht="42" customHeight="1">
+      <c r="A86" s="2"/>
+      <c r="B86" s="3"/>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="3"/>
+      <c r="F86" s="3"/>
+      <c r="G86" s="3"/>
+      <c r="H86" s="3"/>
+      <c r="I86" s="4"/>
+      <c r="J86" s="4"/>
+      <c r="K86" s="4"/>
+      <c r="L86" s="4"/>
+      <c r="M86" s="5"/>
+      <c r="N86" s="6"/>
+    </row>
+    <row r="87" spans="1:14" ht="42" customHeight="1">
+      <c r="A87" s="2"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="3"/>
+      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="4"/>
+      <c r="J87" s="4"/>
+      <c r="K87" s="4"/>
+      <c r="L87" s="4"/>
+      <c r="M87" s="5"/>
+      <c r="N87" s="6"/>
+    </row>
+    <row r="88" spans="1:14" ht="42" customHeight="1">
+      <c r="A88" s="2"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="4"/>
+      <c r="J88" s="4"/>
+      <c r="K88" s="4"/>
+      <c r="L88" s="4"/>
+      <c r="M88" s="5"/>
+      <c r="N88" s="6"/>
+    </row>
+    <row r="89" spans="1:14" ht="42" customHeight="1">
+      <c r="A89" s="2"/>
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3"/>
+      <c r="E89" s="3"/>
+      <c r="F89" s="3"/>
+      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="4"/>
+      <c r="J89" s="4"/>
+      <c r="K89" s="4"/>
+      <c r="L89" s="4"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="6"/>
+    </row>
+    <row r="90" spans="1:14" ht="42" customHeight="1">
+      <c r="A90" s="2"/>
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3"/>
+      <c r="E90" s="3"/>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="4"/>
+      <c r="J90" s="4"/>
+      <c r="K90" s="4"/>
+      <c r="L90" s="4"/>
+      <c r="M90" s="5"/>
+      <c r="N90" s="6"/>
+    </row>
+    <row r="91" spans="1:14" ht="42" customHeight="1">
+      <c r="A91" s="2"/>
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3"/>
+      <c r="E91" s="3"/>
+      <c r="F91" s="3"/>
+      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="5"/>
+      <c r="N91" s="6"/>
+    </row>
+    <row r="92" spans="1:14" ht="42" customHeight="1">
+      <c r="A92" s="2"/>
+      <c r="B92" s="3"/>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3"/>
+      <c r="E92" s="3"/>
+      <c r="F92" s="3"/>
+      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="4"/>
+      <c r="J92" s="4"/>
+      <c r="K92" s="4"/>
+      <c r="L92" s="4"/>
+      <c r="M92" s="5"/>
+      <c r="N92" s="6"/>
+    </row>
+    <row r="93" spans="1:14" ht="42" customHeight="1">
+      <c r="A93" s="2"/>
+      <c r="B93" s="3"/>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3"/>
+      <c r="E93" s="3"/>
+      <c r="F93" s="3"/>
+      <c r="G93" s="3"/>
+      <c r="H93" s="3"/>
+      <c r="I93" s="4"/>
+      <c r="J93" s="4"/>
+      <c r="K93" s="4"/>
+      <c r="L93" s="4"/>
+      <c r="M93" s="5"/>
+      <c r="N93" s="6"/>
+    </row>
+    <row r="94" spans="1:14" ht="42" customHeight="1">
+      <c r="A94" s="2"/>
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="4"/>
+      <c r="J94" s="4"/>
+      <c r="K94" s="4"/>
+      <c r="L94" s="4"/>
+      <c r="M94" s="5"/>
+      <c r="N94" s="6"/>
+    </row>
+    <row r="95" spans="1:14" ht="42" customHeight="1">
+      <c r="A95" s="2"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="3"/>
+      <c r="I95" s="4"/>
+      <c r="J95" s="4"/>
+      <c r="K95" s="4"/>
+      <c r="L95" s="4"/>
+      <c r="M95" s="5"/>
+      <c r="N95" s="6"/>
+    </row>
+    <row r="96" spans="1:14" ht="42" customHeight="1">
+      <c r="A96" s="2"/>
+      <c r="B96" s="3"/>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3"/>
+      <c r="E96" s="3"/>
+      <c r="F96" s="3"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="3"/>
+      <c r="I96" s="4"/>
+      <c r="J96" s="4"/>
+      <c r="K96" s="4"/>
+      <c r="L96" s="4"/>
+      <c r="M96" s="5"/>
+      <c r="N96" s="6"/>
+    </row>
+    <row r="97" spans="1:14" ht="42" customHeight="1">
+      <c r="A97" s="2"/>
+      <c r="B97" s="3"/>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3"/>
+      <c r="E97" s="3"/>
+      <c r="F97" s="3"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="3"/>
+      <c r="I97" s="4"/>
+      <c r="J97" s="4"/>
+      <c r="K97" s="4"/>
+      <c r="L97" s="4"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="6"/>
+    </row>
+    <row r="98" spans="1:14" ht="42" customHeight="1">
+      <c r="A98" s="2"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="5"/>
+      <c r="N98" s="6"/>
+    </row>
+    <row r="99" spans="1:14" ht="42" customHeight="1">
+      <c r="A99" s="2"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
+      <c r="E99" s="3"/>
+      <c r="F99" s="3"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="3"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="5"/>
+      <c r="N99" s="6"/>
+    </row>
+    <row r="100" spans="1:14" ht="42" customHeight="1">
+      <c r="A100" s="2"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
+      <c r="E100" s="3"/>
+      <c r="F100" s="3"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="3"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="5"/>
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="1:14" ht="42" customHeight="1">
+      <c r="A101" s="2"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
+      <c r="E101" s="3"/>
+      <c r="F101" s="3"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="5"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" ht="42" customHeight="1">
+      <c r="A102" s="2"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
+      <c r="E102" s="3"/>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="3"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="5"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" ht="42" customHeight="1">
+      <c r="A103" s="2"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="5"/>
+      <c r="N103" s="6"/>
+    </row>
+    <row r="104" spans="1:14" ht="42" customHeight="1">
+      <c r="A104" s="2"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="3"/>
+      <c r="G104" s="3"/>
+      <c r="H104" s="3"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="6"/>
+    </row>
+    <row r="105" spans="1:14" ht="42" customHeight="1">
+      <c r="A105" s="2"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="3"/>
+      <c r="G105" s="3"/>
+      <c r="H105" s="3"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="6"/>
+    </row>
+    <row r="106" spans="1:14" ht="42" customHeight="1">
+      <c r="A106" s="2"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="3"/>
+      <c r="G106" s="3"/>
+      <c r="H106" s="3"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="6"/>
+    </row>
+    <row r="107" spans="1:14" ht="42" customHeight="1">
+      <c r="A107" s="2"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
+      <c r="H107" s="3"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="5"/>
+      <c r="N107" s="6"/>
+    </row>
+    <row r="108" spans="1:14" ht="42" customHeight="1">
+      <c r="A108" s="2"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="3"/>
+      <c r="G108" s="3"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="6"/>
+    </row>
+    <row r="109" spans="1:14" ht="42" customHeight="1">
+      <c r="A109" s="2"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="3"/>
+      <c r="G109" s="3"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="6"/>
+    </row>
+    <row r="110" spans="1:14" ht="42" customHeight="1">
+      <c r="A110" s="2"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="6"/>
+    </row>
+    <row r="111" spans="1:14" ht="42" customHeight="1">
+      <c r="A111" s="2"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="6"/>
+    </row>
+    <row r="112" spans="1:14" ht="42" customHeight="1">
+      <c r="A112" s="2"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
+      <c r="E112" s="3"/>
+      <c r="F112" s="3"/>
+      <c r="G112" s="3"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="5"/>
+      <c r="N112" s="6"/>
+    </row>
+    <row r="113" spans="1:14" ht="42" customHeight="1">
+      <c r="A113" s="2"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="5"/>
+      <c r="N113" s="6"/>
+    </row>
+    <row r="114" spans="1:14" ht="42" customHeight="1">
+      <c r="A114" s="2"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="5"/>
+      <c r="N114" s="6"/>
+    </row>
+    <row r="115" spans="1:14" ht="42" customHeight="1">
+      <c r="A115" s="2"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="5"/>
+      <c r="N115" s="6"/>
+    </row>
+    <row r="116" spans="1:14" ht="42" customHeight="1">
+      <c r="A116" s="2"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
+      <c r="E116" s="3"/>
+      <c r="F116" s="3"/>
+      <c r="G116" s="3"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="5"/>
+      <c r="N116" s="6"/>
+    </row>
+    <row r="117" spans="1:14" ht="42" customHeight="1">
+      <c r="A117" s="2"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
+      <c r="E117" s="3"/>
+      <c r="F117" s="3"/>
+      <c r="G117" s="3"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="6"/>
+    </row>
+    <row r="118" spans="1:14" ht="42" customHeight="1">
+      <c r="A118" s="2"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="4"/>
+      <c r="J118" s="4"/>
+      <c r="K118" s="4"/>
+      <c r="L118" s="4"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="6"/>
+    </row>
+    <row r="119" spans="1:14" ht="42" customHeight="1">
+      <c r="A119" s="2"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="4"/>
+      <c r="J119" s="4"/>
+      <c r="K119" s="4"/>
+      <c r="L119" s="4"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="6"/>
+    </row>
+    <row r="120" spans="1:14" ht="42" customHeight="1">
+      <c r="A120" s="7"/>
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="8"/>
+      <c r="G120" s="8"/>
+      <c r="H120" s="8"/>
+      <c r="I120" s="9"/>
+      <c r="J120" s="9"/>
+      <c r="K120" s="9"/>
+      <c r="L120" s="9"/>
+      <c r="M120" s="10"/>
+      <c r="N120" s="11"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="K2:K120">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="通过"/>
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="失败"/>
+    <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="阻塞"/>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="K2:K120" xr:uid="{65DB0566-AA76-433F-9311-D4105CE23171}">
+      <formula1>"未执行,通过,失败,阻塞"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J2:J120" xr:uid="{D77D3D1C-0435-4DCE-97B0-3EB55BEC2B6F}">
+      <formula1>"是,否,待确认"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I2:I120" xr:uid="{E4D9ADDA-448D-4B89-B1D7-EC5A9FF1D480}">
+      <formula1>"P0,P1,P2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J2:J5" xr:uid="{CE77779F-19C7-4FCC-B0EB-3DA0A14161BF}">
+      <formula1>"是,否"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>